--- a/docs/Permission-Groups-Summary.xlsx
+++ b/docs/Permission-Groups-Summary.xlsx
@@ -356,8 +356,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="T_AuditLog" displayName="T_AuditLog" ref="A1:D26" headerRowCount="1">
-  <autoFilter ref="A1:D26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="T_AuditLog" displayName="T_AuditLog" ref="A1:D28" headerRowCount="1">
+  <autoFilter ref="A1:D28"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Group"/>
     <tableColumn id="2" name="Permission"/>
@@ -369,8 +369,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_BackendPerms" displayName="T_BackendPerms" ref="A1:C90" headerRowCount="1">
-  <autoFilter ref="A1:C90"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T_BackendPerms" displayName="T_BackendPerms" ref="A1:C92" headerRowCount="1">
+  <autoFilter ref="A1:C92"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Backend Permission Key"/>
     <tableColumn id="2" name="Module"/>
@@ -3194,7 +3194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3728,6 +3728,50 @@
       <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Group administration is a User &amp; Access Administration concern; added to that domain group and to Full (which unions all domains).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Backend Permissions catalog</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>user:change_role_protected, user:update_status_protected</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>added</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Moving PROTECTED_TARGET_ROLE_NAMES (a hardcoded role-name check in user_management_service.py blocking anyone from changing a Tenant Admin/Product Admin target's role or status) from a code-level absolute block to a permission-gated capability, consistent with the project's move from role-based to permission-based control. Deliberate decision: Product Admin is NOT kept as a hardcoded exception -- both target tiers are unlocked by holding this permission. Self-escalation prevention and minimum-admin-count protection (must always keep at least 2 admins, not just 1, so no single admin can unilaterally reduce the pool to just themselves) remain absolute, code-level invariants regardless of this permission -- not yet implemented, service layer still to be written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Group assignment</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>user:change_role_protected, user:update_status_protected</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>Deliberately not assigned to any group yet. Which group(s) should hold this is a separate, still-open decision -- likely warrants its own especially exclusive tier rather than folding into the existing Tenant Admin group set.</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5280,6 +5324,40 @@
       <c r="C90" s="16" t="inlineStr">
         <is>
           <t>Remove a group from a role's eligibility (role_groups)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>user:change_role_protected</t>
+        </is>
+      </c>
+      <c r="B91" s="16" t="inlineStr">
+        <is>
+          <t>Users</t>
+        </is>
+      </c>
+      <c r="C91" s="16" t="inlineStr">
+        <is>
+          <t>Change the role of a protected-tier target (Tenant Admin / Product Admin). Replaces the old unconditional PROTECTED_TARGET_ROLE_NAMES code-level block -- holding this permission is what unlocks the action now, not a hardcoded exception.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>user:update_status_protected</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>Users</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>Activate or deactivate a protected-tier target (Tenant Admin / Product Admin). Same replacement as user:change_role_protected -- permission-gated, not hardcoded.</t>
         </is>
       </c>
     </row>
